--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates C5 ext" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theorems" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP scorecard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v2_theorems" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v2_campaigns" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8177,4 +8179,428 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Теорема</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Кампания</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ключевое число</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T11 уникальность теплового следа</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>доказано+измерено</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>r_H7=1.000, r_EF=0.999</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T12 классификация ко-локации</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>доказано+измерено</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>resid 4.4e-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T13 счётный закон α=1/3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>измерено (закон)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N₀=2L−6·[L≡0 mod 12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T14 полоса T=5000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>измерено</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N=4520=N_strip, S=0.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T15 слепые семейства</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>измерено</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20 ворот, |r_H7|≤0.040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T16 таксономия аттрактора</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>измерено</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>97/18/6, выбросов 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T17 скрученная следовая формула</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>доказано+верифицировано</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>|ΔK|≤9.6e-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T18 квантовое эхо локальности</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>измерено</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S_A 12–16 vs 160–220</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Папка</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C9_nonlocal_trace</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>нелокальный след (R1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>примитив существует; стена локальности</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C10_phase_coded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>жёсткая ко-локация (R2)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>спектр слеп; χ4 калибровочно тривиальна</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C11_alpha_third</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>α=1/3 vs арифметика (R3)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>закон T13 подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C12_band_5000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>полоса T=5000 (R4)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RH верифицирована, N=4520</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C13_blind_families</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>слепые семейства (R5)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>все в нулевой зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C14_anomaly_hunt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>поиск аномалий</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>аттрактор глобален</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C15_dirichlet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Дирихле L (T17)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>разрыв Г2 универсален</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C16_qinfo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>квантовый слой</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>локальность давит запутанность</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -12,8 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates C5 ext" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theorems" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP scorecard" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v2_theorems" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v2_campaigns" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8106,7 +8104,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>9–10 порядков (C3); ≈0.5 порядка (C4); |r_H7| ≤ 0.043 (C5)</t>
+          <t>уровень суррогатного нуля по D_nn (C3); ≈0.5 порядка по невязке (C4); |r_H7| ≤ 0.043 (C5)</t>
         </is>
       </c>
     </row>
@@ -8173,430 +8171,6 @@
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ψ 0.972 у нулей; нулевая зона у затворов</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Теорема</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Кампания</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Ключевое число</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T11 уникальность теплового следа</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>доказано+измерено</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>r_H7=1.000, r_EF=0.999</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T12 классификация ко-локации</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>доказано+измерено</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resid 4.4e-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T13 счётный закон α=1/3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>измерено (закон)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N₀=2L−6·[L≡0 mod 12]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T14 полоса T=5000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>измерено</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N=4520=N_strip, S=0.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T15 слепые семейства</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>измерено</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20 ворот, |r_H7|≤0.040</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T16 таксономия аттрактора</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>измерено</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>97/18/6, выбросов 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T17 скрученная следовая формула</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>доказано+верифицировано</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>|ΔK|≤9.6e-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T18 квантовое эхо локальности</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>измерено</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>S_A 12–16 vs 160–220</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Папка</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Предмет</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Вердикт</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C9_nonlocal_trace</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>нелокальный след (R1)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>примитив существует; стена локальности</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C10_phase_coded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>жёсткая ко-локация (R2)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>спектр слеп; χ4 калибровочно тривиальна</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C11_alpha_third</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>α=1/3 vs арифметика (R3)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>закон T13 подтверждён</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>C12_band_5000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>полоса T=5000 (R4)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RH верифицирована, N=4520</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C13_blind_families</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>слепые семейства (R5)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>все в нулевой зоне</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>C14_anomaly_hunt</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>поиск аномалий</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>аттрактор глобален</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>C15_dirichlet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Дирихле L (T17)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>разрыв Г2 универсален</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>C16_qinfo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>квантовый слой</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>локальность давит запутанность</t>
         </is>
       </c>
     </row>

--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>0.2584614616101241</t>
+          <t>0.007914719356298686</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0.1076923076923077</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>0.2584614616101241</t>
+          <t>0.007914719356298686</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>0.1076923076923077</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0.27294093962689137</t>
+          <t>0.008015280259706855</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0.6615384615384615</t>
+          <t>0.7846153846153846</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>0.26646412211825615</t>
+          <t>0.007478249568408766</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.015384615384615385</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>0.25756116766269066</t>
+          <t>0.00792562967836877</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0.09230769230769231</t>
+          <t>0.4461538461538462</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>0.26290030602178477</t>
+          <t>0.008783298566854947</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>0.26153846153846155</t>
+          <t>0.5846153846153846</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>0.27283900590796833</t>
+          <t>0.007221531153910559</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0.6615384615384615</t>
+          <t>0.03076923076923077</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>0.27742356502892235</t>
+          <t>0.007120868762930811</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>0.8461538461538461</t>
+          <t>0.03076923076923077</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>0.2765285060305515</t>
+          <t>0.008551944077678841</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.35384615384615387</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>0.2684784332409849</t>
+          <t>0.007812660576904646</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>0.5076923076923077</t>
+          <t>0.07692307692307693</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>0.2559194498960368</t>
+          <t>0.006937508455596089</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0.09230769230769231</t>
+          <t>0.015384615384615385</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>0.27898866994021687</t>
+          <t>0.007019143656421178</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>0.8615384615384616</t>
+          <t>0.046153846153846156</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>0.23783037032567297</t>
+          <t>0.008012206363652071</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0.015384615384615385</t>
+          <t>0.06153846153846154</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>0.23783037032567297</t>
+          <t>0.008012206363652071</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>0.015384615384615385</t>
+          <t>0.06153846153846154</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>0.27364979930305006</t>
+          <t>0.007653914181462794</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>0.676923076923077</t>
+          <t>0.12307692307692308</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>0.2744737752798627</t>
+          <t>0.007640358103802026</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>0.7230769230769231</t>
+          <t>0.09230769230769231</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>0.2438168902794245</t>
+          <t>0.007975236655588887</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>0.015384615384615385</t>
+          <t>0.06153846153846154</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>0.2645152200671169</t>
+          <t>0.007429650718609349</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>0.3230769230769231</t>
+          <t>0.24615384615384617</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>0.2672149647436652</t>
+          <t>0.007805446136114553</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>0.4153846153846154</t>
+          <t>0.1076923076923077</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>0.2760685312338192</t>
+          <t>0.007713265850315169</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>0.7692307692307693</t>
+          <t>0.07692307692307693</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>0.24341566745350462</t>
+          <t>0.008024072383063996</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>0.015384615384615385</t>
+          <t>0.24615384615384617</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.2667970103192488</t>
+          <t>0.008046068940227967</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.47692307692307695</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>0.2841371537519926</t>
+          <t>0.007535212943822891</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.4461538461538462</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>0.25986533806877465</t>
+          <t>0.008256299984826148</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>0.13846153846153847</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>0.2739162175842987</t>
+          <t>0.007853097614160887</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>0.6923076923076923</t>
+          <t>0.18461538461538463</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>0.26923860380250564</t>
+          <t>0.006977114691933522</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>0.5538461538461539</t>
+          <t>0.4461538461538462</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>0.27486345899335307</t>
+          <t>0.008700459335991041</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>0.7230769230769231</t>
+          <t>0.015384615384615385</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>0.26750629816898547</t>
+          <t>0.007176120773537391</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>0.4307692307692308</t>
+          <t>0.47692307692307695</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>0.27890189438403135</t>
+          <t>0.008450121155358693</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>0.8615384615384616</t>
+          <t>0.13846153846153847</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>0.27225166805582063</t>
+          <t>0.007836347085398014</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>0.6307692307692307</t>
+          <t>0.6153846153846154</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>0.2679360249714036</t>
+          <t>0.008394410923006529</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>0.47692307692307695</t>
+          <t>0.5846153846153846</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>0.26681296898010226</t>
+          <t>0.007409887472070874</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.06153846153846154</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>0.2680820836243925</t>
+          <t>0.0070198547528949546</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>0.49230769230769234</t>
+          <t>0.24615384615384617</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>0.2945726339274234</t>
+          <t>0.008347786349227214</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.015384615384615385</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>0.26266111267600395</t>
+          <t>0.009221555365816578</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>0.23076923076923078</t>
+          <t>0.046153846153846156</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.2946466564180682</t>
+          <t>0.007985529315771291</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.09230769230769231</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>0.28415591786755534</t>
+          <t>0.00885888650879578</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9692307692307692</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>0.278623427642229</t>
+          <t>0.007329524109823638</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>0.8615384615384616</t>
+          <t>0.046153846153846156</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>0.2746151368213678</t>
+          <t>0.008493316495026338</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>0.7230769230769231</t>
+          <t>0.27692307692307694</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>0.2697924253624715</t>
+          <t>0.008489595735260718</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>0.2876975019927567</t>
+          <t>0.007213956575646643</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.03076923076923077</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>0.2701032374078391</t>
+          <t>0.006971979348454871</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.03076923076923077</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>0.2739785553296452</t>
+          <t>0.00702576420141725</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0.6923076923076923</t>
+          <t>0.15384615384615385</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>0.27400288270718043</t>
+          <t>0.007331287968436786</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>0.6923076923076923</t>
+          <t>0.15384615384615385</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>0.27263360198663134</t>
+          <t>0.00834817330955571</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>0.6615384615384615</t>
+          <t>0.8307692307692308</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0.2718209709083901</t>
+          <t>0.007401691893929261</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>0.6153846153846154</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>0.25605730927549486</t>
+          <t>0.007198018197299075</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>0.09230769230769231</t>
+          <t>0.12307692307692308</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>0.27687716340824475</t>
+          <t>0.008236590752331439</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>0.8153846153846154</t>
+          <t>0.13846153846153847</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>0.2802756650279252</t>
+          <t>0.008312923413609974</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>0.9076923076923077</t>
+          <t>0.09230769230769231</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>0.2772393680958689</t>
+          <t>0.007459168342779594</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>0.8307692307692308</t>
+          <t>0.38461538461538464</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>0.2765602557322508</t>
+          <t>0.008678094906247585</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7846153846153846</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>0.27362384723551714</t>
+          <t>0.008471276094648513</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>0.676923076923077</t>
+          <t>0.015384615384615385</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">

--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.0434730569109078</v>
+        <v>0.09722433888689566</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4525,12 +4525,15 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>35 новых затворов (6 ручек) + 2 декуя; |r_H7| ≤ 0.043, ⟨r⟩ = 0.500±0.001</t>
+          <t>35 новых затворов (6 ручек) + 2 декуя (v2.0.5): ⟨r⟩ = 0.569–0.633 (полоса GUE 0.5996±0.03, среднее 0.601); |r_H7| ≤ 0.097</t>
         </is>
       </c>
     </row>
@@ -4635,6 +4638,21 @@
           <t>twist</t>
         </is>
       </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>p_r</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>r_EF_raw</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>gue_class</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4674,17 +4692,17 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>0.5002209850116544</t>
+          <t>0.5885498536788939</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>0.0026159927603893614</t>
+          <t>0.05019545150959459</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>0.8085330835421941</t>
+          <t>0.7542505855265528</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -4694,22 +4712,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>0.016118052618777166</t>
+          <t>0.016338396534999782</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>-0.04264554889549053</t>
+          <t>0.03545042281947057</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>0.3122140153403541</t>
+          <t>0.2874546977409112</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2.7262665691346006</t>
+          <t>2.5005685012493744</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -4717,6 +4735,21 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>0.3230769230769231</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>0.8069844357762034</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4756,17 +4789,17 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>0.4992803588243496</t>
+          <t>0.5971104110620721</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>-0.009175564895316103</t>
+          <t>0.014939867065069442</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>0.7049044786577833</t>
+          <t>0.6719970329024003</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -4776,22 +4809,22 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>0.01681707448689878</t>
+          <t>0.017044436057937606</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>-0.0360080290773594</t>
+          <t>0.03691806967225179</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>0.2747361314996458</t>
+          <t>0.2740746092913692</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>2.69681495364616</t>
+          <t>2.3171754759485768</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -4799,6 +4832,21 @@
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>0.6461538461538462</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>0.7032148077710272</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4834,17 +4882,17 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>0.5002879955120584</t>
+          <t>0.607940136141334</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>8.334933248494393e-05</t>
+          <t>-0.002124672545840933</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.9783814903667243</t>
+          <t>0.9532094269680216</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4854,22 +4902,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>0.012483008484912569</t>
+          <t>0.012662357624376076</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>-0.052348295217382275</t>
+          <t>0.017455233937912994</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>0.401713785638636</t>
+          <t>0.31337786809404605</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2.565831252082809</t>
+          <t>2.986025141856172</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -4881,6 +4929,21 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>0.977725212241528</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4916,17 +4979,17 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>0.5010657624581877</t>
+          <t>0.5898800825542043</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>-0.033538109401047046</t>
+          <t>0.04827457462127953</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>0.9593366341981692</t>
+          <t>0.9644992270884365</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -4936,22 +4999,22 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>0.012502844609119204</t>
+          <t>0.01268329040900549</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>-0.05281507253352243</t>
+          <t>0.006654363580627631</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>0.3949623048673599</t>
+          <t>0.32735690776958715</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>2.562653940030055</t>
+          <t>2.925995574781015</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -4963,6 +5026,21 @@
       <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>0.13846153846153847</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>0.958401320357481</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4998,17 +5076,17 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>0.5006240994139937</t>
+          <t>0.6152383412197607</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>0.018988358449378486</t>
+          <t>0.025611938617624775</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0.9911878822153721</t>
+          <t>0.8783046048967106</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -5018,22 +5096,22 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>0.013471305471765982</t>
+          <t>0.013661235138093515</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>-0.053775440777919535</t>
+          <t>-0.01920358032033344</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>0.4256415170672883</t>
+          <t>0.32473061259338687</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>2.455031478585997</t>
+          <t>2.7638545625535573</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
@@ -5045,6 +5123,21 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>0.5230769230769231</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>0.9908559404315818</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5080,17 +5173,17 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>0.5003439509109904</t>
+          <t>0.607998673224463</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>0.01448110766274665</t>
+          <t>0.02301775825381165</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>0.9865888932396799</t>
+          <t>0.5101253482860982</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -5100,22 +5193,22 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>0.013564496517157335</t>
+          <t>0.013755293154195242</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>-0.05374945104522152</t>
+          <t>-0.04084664488118987</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>0.4378757239461365</t>
+          <t>0.2694800229440199</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>2.375875819078005</t>
+          <t>2.0445745370956256</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -5127,6 +5220,21 @@
       <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>0.5538461538461539</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>0.9864726684580418</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -5162,17 +5270,17 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>0.49937519707986044</t>
+          <t>0.6228553971148943</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>0.03256480942017184</t>
+          <t>0.02943866803244155</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.9528092744011389</t>
+          <t>0.9621987203264782</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -5182,22 +5290,22 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>0.012146051557109669</t>
+          <t>0.012323189092906537</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>-0.05240775684037597</t>
+          <t>-0.0021549802773196997</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>0.3918989896543287</t>
+          <t>0.32148673735086525</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2.5649901065786325</t>
+          <t>2.9996686910020753</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
@@ -5209,6 +5317,21 @@
       </c>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>0.4461538461538462</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>0.9518057719721488</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5244,17 +5367,17 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>0.499673927747255</t>
+          <t>0.593351691206167</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0.013158515353369097</t>
+          <t>0.055518742904844515</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>0.5473567199177879</t>
+          <t>0.3628997527092929</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -5264,22 +5387,22 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>0.01648378391901257</t>
+          <t>0.016705553083536766</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>-0.02197833452424172</t>
+          <t>0.034093253005591094</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>0.16472360888163798</t>
+          <t>0.21559592291421179</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>3.4563051301961507</t>
+          <t>1.52510536961563</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr"/>
@@ -5291,6 +5414,21 @@
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>0.27692307692307694</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>0.5462671125207164</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -5330,17 +5468,17 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>0.5007636268946912</t>
+          <t>0.6204598866505948</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>0.02956837278993612</t>
+          <t>0.010090128050210954</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0.7547061660271625</t>
+          <t>0.8095537781173744</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -5350,22 +5488,22 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>0.022131817056104335</t>
+          <t>0.022431179466211412</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>-0.04127812688104556</t>
+          <t>0.010391086002908528</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>0.33265024041158636</t>
+          <t>0.2837710961692556</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2.392856508756287</t>
+          <t>2.8162230153200816</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -5377,6 +5515,21 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>0.7538461538461538</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>0.7528600901351147</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -5416,17 +5569,17 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>0.49977776466772744</t>
+          <t>0.5903370791626549</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>-0.02571953033031348</t>
+          <t>0.022787712835965892</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>0.7137610745140623</t>
+          <t>0.6559656667883534</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -5436,22 +5589,22 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>0.016519214464733943</t>
+          <t>0.016742673873703772</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>-0.036212263823706896</t>
+          <t>0.012550478283105132</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>0.2693135532122333</t>
+          <t>0.2617039473272364</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>2.7847589896329894</t>
+          <t>2.4585612677088036</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -5463,6 +5616,21 @@
       <c r="R13" s="4" t="inlineStr"/>
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>0.5076923076923077</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>0.7121315360810689</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -5498,17 +5666,17 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>0.5001023489130423</t>
+          <t>0.6186477529303885</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>-0.00032743111548351846</t>
+          <t>-0.0027446817789540854</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0.9795345692536618</t>
+          <t>0.9582161082309572</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -5518,22 +5686,22 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>0.012503588590894399</t>
+          <t>0.012683132491760469</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>-0.05243624373512939</t>
+          <t>-0.015564081467851305</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>0.4028022745908379</t>
+          <t>0.2973625610721723</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>2.5619786135444635</t>
+          <t>3.274723577130021</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -5549,6 +5717,21 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>0.8307692307692308</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>0.9788919784490557</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -5584,17 +5767,17 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>0.499673927747255</t>
+          <t>0.593351691206167</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>0.013158515353369097</t>
+          <t>0.055518742904844515</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>0.5473567199177879</t>
+          <t>0.3628997527092929</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -5604,22 +5787,22 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>0.01648378391901257</t>
+          <t>0.016705553083536766</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>-0.02197833452424172</t>
+          <t>0.020760693198588167</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>0.16472360888163798</t>
+          <t>0.21616500076552964</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>3.4563051301961507</t>
+          <t>1.5827680628179812</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr"/>
@@ -5635,6 +5818,21 @@
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>0.27692307692307694</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>0.5462671125207164</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -5670,17 +5868,17 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>0.5001802215846869</t>
+          <t>0.6220725257190568</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>-0.025928166932588724</t>
+          <t>0.013518745343993955</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>0.48494860263351935</t>
+          <t>0.532999835524859</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -5690,22 +5888,22 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>0.019279522155285403</t>
+          <t>0.01953732296098002</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>-0.02147815546724698</t>
+          <t>0.011302593914652473</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>0.21918548629680826</t>
+          <t>0.2281800851351252</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2.3104940325062975</t>
+          <t>2.2863399376035134</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
@@ -5713,6 +5911,21 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>0.4832932983073996</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -5748,17 +5961,17 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>0.4998874217759936</t>
+          <t>0.6076362889457331</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>-0.02549178079192375</t>
+          <t>0.05230482663052002</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>0.9140565197266527</t>
+          <t>0.8740281900769412</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -5768,22 +5981,22 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>0.015622099779834035</t>
+          <t>0.01583773195921014</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>-0.04928670513203215</t>
+          <t>-0.010154699608539965</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>0.36219107408509765</t>
+          <t>0.28249206032308055</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>2.659765228317982</t>
+          <t>3.1299389040324135</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
@@ -5795,6 +6008,21 @@
           <t>3.1416_0</t>
         </is>
       </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>0.09230769230769231</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>0.9128380022533084</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -5830,17 +6058,17 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>0.4981432516739636</t>
+          <t>0.6037762602966783</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>0.001815546323399943</t>
+          <t>0.017737200307367564</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>0.7353238723124876</t>
+          <t>0.8261274633645344</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -5850,22 +6078,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>0.01913866064852017</t>
+          <t>0.019396079354432844</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-0.04048633004078254</t>
+          <t>-0.004445601483066153</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>0.33907044559472094</t>
+          <t>0.27976975818213023</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2.2880502044125928</t>
+          <t>2.9687735738288663</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
@@ -5877,6 +6105,21 @@
           <t>0_3.1416</t>
         </is>
       </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>0.5076923076923077</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>0.733346015780428</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5912,17 +6155,17 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>0.49971143168301413</t>
+          <t>0.6046035618579435</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>-0.03301495046331931</t>
+          <t>0.07324539860050897</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>0.22171130539927852</t>
+          <t>0.4405276481785465</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -5932,22 +6175,22 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>0.018657370975669336</t>
+          <t>0.018905437455564788</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>-0.00521413427113084</t>
+          <t>0.020174521350186343</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>0.22505272166285692</t>
+          <t>0.22352045123954864</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>1.0083212413238791</t>
+          <t>1.8806025332235232</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr"/>
@@ -5959,6 +6202,21 @@
           <t>3.1416_3.1416</t>
         </is>
       </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>0.03076923076923077</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>0.22010507498940943</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -5998,17 +6256,17 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>0.49936106761217025</t>
+          <t>0.6019194225600351</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>-0.00963133088534814</t>
+          <t>0.009345250718280951</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>0.7350152409442272</t>
+          <t>0.7760556053639978</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -6018,22 +6276,22 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>0.020584160401008796</t>
+          <t>0.020863667917508294</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>-0.03936237905599177</t>
+          <t>0.007548871177263742</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>0.3213564358845982</t>
+          <t>0.26604895334693857</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>2.4097156102338166</t>
+          <t>2.888591458522185</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr"/>
@@ -6041,6 +6299,21 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>0.6307692307692307</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>0.7331892325799109</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -6080,17 +6353,17 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>0.49912072510331584</t>
+          <t>0.5883705867556217</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>0.006168202581172419</t>
+          <t>0.09722433888689566</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>0.7598877738481652</t>
+          <t>0.6814741872895872</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -6100,22 +6373,22 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>0.016558286790881123</t>
+          <t>0.016781839811007417</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>-0.03971900946350914</t>
+          <t>0.007294151996916612</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>0.2805476964852226</t>
+          <t>0.2708598368849609</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>2.8501634243637155</t>
+          <t>2.489036555017225</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr"/>
@@ -6123,6 +6396,21 @@
       <c r="R21" s="4" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>0.15384615384615385</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>0.7583076925194805</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -6158,17 +6446,17 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>0.4984806414127237</t>
+          <t>0.5774983938339029</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>-0.004101930954335956</t>
+          <t>0.00723384599975903</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>0.30177529122345886</t>
+          <t>0.531582101400729</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -6178,22 +6466,22 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>0.021315061388450768</t>
+          <t>0.021597822342189477</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>-0.011537402563448021</t>
+          <t>0.0170628255254047</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>0.23797631621946858</t>
+          <t>0.22432775398356597</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>1.316570904047279</t>
+          <t>2.293605078901728</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -6205,6 +6493,21 @@
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>0.4307692307692308</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>0.2999438054421877</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -6240,17 +6543,17 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>0.49914109754983166</t>
+          <t>0.5735693706194834</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>-0.0032450080359435383</t>
+          <t>-0.0027162642678458656</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>0.8401687722534923</t>
+          <t>0.756644455306834</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -6260,22 +6563,22 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>0.012860543659165643</t>
+          <t>0.013045436274541057</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>-0.043963522446303076</t>
+          <t>0.005741279162543069</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>0.3262473818835146</t>
+          <t>0.2576037336401608</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>2.710005792523023</t>
+          <t>2.914954552612214</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -6287,6 +6590,21 @@
       <c r="R23" s="4" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>0.838768057056977</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -6322,17 +6640,17 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>0.5004089002227807</t>
+          <t>0.6195495456836023</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>-0.02600021962385021</t>
+          <t>0.011988475462252143</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.41821975928938765</t>
+          <t>0.535779887083524</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6342,22 +6660,22 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>0.020097634537947308</t>
+          <t>0.020365805846256933</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>-0.01805955916054558</t>
+          <t>0.015337730398458399</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>0.22430502088855472</t>
+          <t>0.23109970540258126</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>1.945026984780235</t>
+          <t>2.2520243190204106</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr"/>
@@ -6369,6 +6687,21 @@
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>0.6307692307692307</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>0.4164827894249051</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -6404,17 +6737,17 @@
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>0.5001802215846869</t>
+          <t>0.6220725257190568</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-0.025928166932588724</t>
+          <t>0.013518745343993955</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>0.48494860263351935</t>
+          <t>0.532999835524859</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -6424,22 +6757,22 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>0.019279522155285403</t>
+          <t>0.01953732296098002</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>-0.02147815546724698</t>
+          <t>0.01348188009591279</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>0.21918548629680826</t>
+          <t>0.22779013531597275</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>2.3104940325062975</t>
+          <t>2.2806868028253784</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr"/>
@@ -6451,6 +6784,21 @@
       </c>
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>0.4832932983073996</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6486,17 +6834,17 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>0.4985422888635022</t>
+          <t>0.583386141304597</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>0.007999089933803834</t>
+          <t>0.0034448825510727654</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>0.7245521963637754</t>
+          <t>0.8781537622771927</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -6506,22 +6854,22 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>0.020545879750600342</t>
+          <t>0.020821916625537496</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>-0.0412292558837871</t>
+          <t>-0.010638422786441433</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>0.36818265146369233</t>
+          <t>0.28388941864910544</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>2.0798955333806073</t>
+          <t>3.130768977910388</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr"/>
@@ -6533,6 +6881,21 @@
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>0.7692307692307693</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>0.7224245280388379</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -6568,17 +6931,17 @@
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>0.4991526490906031</t>
+          <t>0.6046181830344813</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>-0.01904676047596791</t>
+          <t>0.059166394208368674</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>0.29980899884805157</t>
+          <t>0.40890422877633176</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -6588,22 +6951,22 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>0.018100749578567655</t>
+          <t>0.01834192137445767</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>-0.008735648197283424</t>
+          <t>0.015154993624285488</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>0.19549536320627806</t>
+          <t>0.21899373914312983</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>1.5782709215449389</t>
+          <t>1.797993114746992</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr"/>
@@ -6619,6 +6982,21 @@
           <t>3.1416_3.1416</t>
         </is>
       </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>0.046153846153846156</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>0.2983518599461418</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6658,17 +7036,17 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>0.501781280554399</t>
+          <t>0.582602154043896</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>0.022340393841273985</t>
+          <t>0.0678132356490143</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>0.12464846309369622</t>
+          <t>0.22137590462185164</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -6678,22 +7056,22 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0.018039266449016086</t>
+          <t>0.018279227921039573</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>0.0021899628759374373</t>
+          <t>0.021311456234926814</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>0.18771506919718692</t>
+          <t>0.22372586892278448</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>0.652363716677009</t>
+          <t>0.8942392283476792</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr"/>
@@ -6705,6 +7083,21 @@
           <t>3.1416_3.1416</t>
         </is>
       </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>0.12307692307692308</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>0.12377685730696834</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -6740,17 +7133,17 @@
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>0.4992371944797412</t>
+          <t>0.6022023808326402</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>-0.0434730569109078</t>
+          <t>0.06954053017452054</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>0.3513754235364971</t>
+          <t>0.2779677270963383</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -6760,22 +7153,22 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>0.017138500090860653</t>
+          <t>0.017367901895018606</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>-0.009722056370383375</t>
+          <t>0.019167074616461936</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>0.12906723550210084</t>
+          <t>0.19243731194727245</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>2.797747069596163</t>
+          <t>1.3448569295687698</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr"/>
@@ -6787,6 +7180,21 @@
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>0.03076923076923077</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>0.3504150378402214</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -6822,17 +7230,17 @@
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>0.49807698531055156</t>
+          <t>0.5690442342807999</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>-0.020807755898881498</t>
+          <t>0.04935166599578614</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>0.8252308389276912</t>
+          <t>0.8569287226622683</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -6842,22 +7250,22 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0.01629901279185895</t>
+          <t>0.016524288679877285</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>-0.04605544915277373</t>
+          <t>-0.0085554355591231</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>0.3483384375578214</t>
+          <t>0.28381953235025426</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>2.5012636968489543</t>
+          <t>3.0494171808912713</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
@@ -6869,6 +7277,21 @@
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>0.8235354302152079</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -6904,17 +7327,17 @@
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>0.49917465448184284</t>
+          <t>0.5956725473891672</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>-0.018555249495665956</t>
+          <t>-0.0043112184500107495</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>0.6922526428120513</t>
+          <t>0.7785858611119407</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -6924,22 +7347,22 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>0.020470461534645573</t>
+          <t>0.020746338153562655</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>-0.037450550242612436</t>
+          <t>-0.0006599247572761591</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>0.3197894131637043</t>
+          <t>0.2685263041420684</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>2.281824109921736</t>
+          <t>2.9019346479253803</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr"/>
@@ -6951,6 +7374,21 @@
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>0.6902772300924926</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6986,17 +7424,17 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>0.4985123648700755</t>
+          <t>0.6016443560478398</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>0.015509222009206304</t>
+          <t>0.036214408774905095</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>-0.6178192952365542</t>
+          <t>-0.6997826778884171</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -7006,22 +7444,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0.02105970406711946</t>
+          <t>0.021338854070066037</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>0.03154846638992883</t>
+          <t>-0.0019464340841955714</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>0.28964644239453546</t>
+          <t>0.24953596061082847</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>-2.241932461721595</t>
+          <t>-2.796535786249075</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
@@ -7033,6 +7471,21 @@
       <c r="R32" s="3" t="inlineStr"/>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>0.3230769230769231</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>-0.615882572649812</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -7068,17 +7521,17 @@
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>0.49991433961490417</t>
+          <t>0.6328438481053176</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>-0.020145526566299678</t>
+          <t>0.017684498031611772</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>0.9419672679132703</t>
+          <t>0.22240767740301876</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -7088,22 +7541,22 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>0.01648243117261485</t>
+          <t>0.016706422042350896</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>-0.052979935188538586</t>
+          <t>-0.03016341812428095</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>0.4029354566314258</t>
+          <t>0.13310516957301163</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>2.4692470884038125</t>
+          <t>1.8975303238598704</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -7115,6 +7568,21 @@
       <c r="R33" s="4" t="inlineStr"/>
       <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="4" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>0.47692307692307695</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>0.9418660680748239</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -7150,17 +7618,17 @@
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>0.49992004873214907</t>
+          <t>0.6101542599904137</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>-0.03159633890199182</t>
+          <t>0.019052239071588716</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>0.20394134947466486</t>
+          <t>-0.47527651221171907</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -7170,22 +7638,22 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0.01460809043926729</t>
+          <t>0.014809962866646978</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>-0.015486709672608623</t>
+          <t>-0.011809483128928358</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>0.3338918979412508</t>
+          <t>0.21672238858992304</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>0.6571829400481064</t>
+          <t>-2.138528613025542</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr"/>
@@ -7197,6 +7665,21 @@
       <c r="R34" s="3" t="inlineStr"/>
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>0.5384615384615384</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>0.20569656602859895</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -7232,17 +7715,17 @@
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>0.4993290098220721</t>
+          <t>0.5974615381898642</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>-0.01083919335483493</t>
+          <t>-0.006518720404643293</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>-0.09058414628317206</t>
+          <t>-0.470285274282095</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -7252,22 +7735,22 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>0.01831235054801953</t>
+          <t>0.018559570562359493</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>-0.0005416443426220311</t>
+          <t>-0.013884663704635517</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>0.252112284191589</t>
+          <t>0.21443948271076074</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>-0.3571523784700771</t>
+          <t>-2.128342247463167</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr"/>
@@ -7279,6 +7762,21 @@
       </c>
       <c r="S35" s="4" t="inlineStr"/>
       <c r="T35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>0.9384615384615385</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>-0.08885867623247186</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7314,17 +7812,17 @@
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>0.4998890048173997</t>
+          <t>0.6164701591703239</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>0.013536724648918108</t>
+          <t>0.05082535021249881</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>0.771226648870061</t>
+          <t>0.721132802918226</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -7334,22 +7832,22 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0.011935527186437093</t>
+          <t>0.0121113513852843</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>-0.039902137466153585</t>
+          <t>0.005977556367944779</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>0.3051513029256952</t>
+          <t>0.2471380779186212</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>2.6581200163963437</t>
+          <t>2.8937477080556198</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr"/>
@@ -7361,6 +7859,21 @@
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>0.015384615384615385</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>0.769643441067695</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -7396,17 +7909,17 @@
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>0.50105914340335</t>
+          <t>0.5915492970807834</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>0.004769635908370549</t>
+          <t>0.03222037307804771</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>0.6839184792207927</t>
+          <t>0.6756444411639951</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -7416,22 +7929,22 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>0.010364966873405742</t>
+          <t>0.010527485356309966</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>0.2456196055314914</t>
+          <t>0.009767318301342273</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>0.14686019644862844</t>
+          <t>0.23707042962169333</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>2.9844633487373677</t>
+          <t>2.80877342621444</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -7443,6 +7956,21 @@
       <c r="R37" s="4" t="inlineStr"/>
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="4" t="inlineStr"/>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>0.03076923076923077</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>0.6822087929040519</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7478,17 +8006,17 @@
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>0.4994727589799313</t>
+          <t>0.5720137072758785</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>-0.02364471020079269</t>
+          <t>0.03859696032446983</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>0.6619679006016338</t>
+          <t>-0.6350975810235754</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -7498,22 +8026,22 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0.016971359693126076</t>
+          <t>0.017201104421957988</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>-0.029270523178301904</t>
+          <t>0.0017465722019571269</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>0.499555297750286</t>
+          <t>0.26140207089816875</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>1.3837075232569485</t>
+          <t>-2.4362628461104285</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr"/>
@@ -7525,6 +8053,21 @@
       </c>
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>0.5230769230769231</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>0.6638095842179609</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -7560,17 +8103,17 @@
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>0.49917465448184284</t>
+          <t>0.5956725473891672</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>-0.018555249495665956</t>
+          <t>-0.0043112184500107495</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>0.6922526428120513</t>
+          <t>0.7785858611119407</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -7580,22 +8123,22 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>0.020470461534645573</t>
+          <t>0.020746338153562655</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>-0.037450550242612436</t>
+          <t>0.012518343420766485</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>0.3197894131637043</t>
+          <t>0.2655574877050779</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>2.281824109921736</t>
+          <t>2.8847520900707995</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr"/>
@@ -7607,6 +8150,21 @@
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>0.6902772300924926</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -7642,17 +8200,17 @@
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>0.4991207837081291</t>
+          <t>0.6102746489308469</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>-0.020663018208646872</t>
+          <t>0.016575824763949303</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>0.9166398479550746</t>
+          <t>-0.5006649409982682</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -7662,22 +8220,22 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0.017158121646748608</t>
+          <t>0.017390614044989698</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>-0.044770389436901016</t>
+          <t>0.0019198362727518034</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>0.47759407887147964</t>
+          <t>0.24583511456617027</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>2.0130279664767174</t>
+          <t>-2.0443978402269365</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr"/>
@@ -7689,6 +8247,21 @@
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>0.6923076923076923</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>0.9175302619923646</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7925,7 +8498,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>|r_H7| ≤ 0.043</t>
+          <t>|r_H7| ≤ 0.226 (C3); ≤ 0.097 (C5)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -8104,7 +8677,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>уровень суррогатного нуля по D_nn (C3); ≈0.5 порядка по невязке (C4); |r_H7| ≤ 0.043 (C5)</t>
+          <t>уровень суррогатного нуля по D_nn (C3); ≈0.5 порядка по невязке (C4); |r_H7| ≤ 0.097 (C5, Бонферрони 0.57)</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8699,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>⟨r⟩ = 0.60 при Nv ≥ 8; вся C5 в классе</t>
+          <t>⟨r⟩ = 0.60 при Nv ≥ 8; вся C5 в классе: ⟨r⟩ = 0.569–0.633, среднее 0.60</t>
         </is>
       </c>
     </row>

--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Г2 — НЕТ</t>
+          <t>Г2 — ранговая ветвь</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Разрыв в следовой метрике</t>
+          <t>Следовая ветвь</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Г2 — НЕТ</t>
+          <t>Г2 — консервативная ветвь</t>
         </is>
       </c>
     </row>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>уровень суррогатного нуля по D_nn (C3); ≈0.5 порядка по невязке (C4); |r_H7| ≤ 0.097 (C5, Бонферрони 0.57)</t>
+          <t>D_nn 0.0079 — уровень самих нулей ζ (сдвинутые окна нулей и GUE-класс нулей: 0.0079±0.0005, C3); семья 0.0069–0.0092 в полосе нулей; класс GUE ⟨r⟩ = 0.60 (C5); следовый мост |ΔK| ≤ 1.2e-5 (C4)</t>
         </is>
       </c>
     </row>

--- a/Hilbert_Polya/tables/hp_workbook.xlsx
+++ b/Hilbert_Polya/tables/hp_workbook.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Г5 — НЕТ</t>
+          <t>Г5 — ДА (лестница сходимости)</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ψ 0.972 у нулей; нулевая зона у затворов</t>
+          <t>лестница сходимости (v2.0.8): ψ-корреляция затворов растёт −0.12 → +0.09 → +0.24 при Nv = 0 → 2 → 16 — максимум в рабочем окне (Vortex-скан: L 24→96, пол GUE 0.0324→0.0220, D = 0.0318); нули 0.972 → 1 по явной формуле; с Г2 = ДА простые входят через тождество уровней; битовая ветвь открыта (T18)</t>
         </is>
       </c>
     </row>
